--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.424718149469041</v>
+        <v>0.8815166992887192</v>
       </c>
       <c r="D2" t="n">
-        <v>5.738056290846415</v>
+        <v>0.9324341472625425</v>
       </c>
       <c r="E2" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F2" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.95405112780683</v>
+        <v>2.59253330826861</v>
       </c>
       <c r="D3" t="n">
-        <v>16.29151703789201</v>
+        <v>2.647371518657452</v>
       </c>
       <c r="E3" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F3" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.15521675461567</v>
+        <v>2.625222722625047</v>
       </c>
       <c r="D4" t="n">
-        <v>16.61410520580724</v>
+        <v>2.699792095943677</v>
       </c>
       <c r="E4" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F4" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.42096222986451</v>
+        <v>2.180906362352983</v>
       </c>
       <c r="D5" t="n">
-        <v>12.63190497039952</v>
+        <v>2.052684557689922</v>
       </c>
       <c r="E5" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F5" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.31153331577209</v>
+        <v>3.463124163812965</v>
       </c>
       <c r="D6" t="n">
-        <v>20.96103092439711</v>
+        <v>3.406167525214531</v>
       </c>
       <c r="E6" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F6" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.29535544960998</v>
+        <v>4.922995260561622</v>
       </c>
       <c r="D7" t="n">
-        <v>30.43146042722066</v>
+        <v>4.945112319423357</v>
       </c>
       <c r="E7" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F7" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.883765980338506</v>
+        <v>1.443611971805007</v>
       </c>
       <c r="D8" t="n">
-        <v>9.120094518329283</v>
+        <v>1.482015359228509</v>
       </c>
       <c r="E8" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F8" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.28317894453272</v>
+        <v>7.033516578486568</v>
       </c>
       <c r="D9" t="n">
-        <v>43.49994888131298</v>
+        <v>7.06874169321336</v>
       </c>
       <c r="E9" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F9" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.26664088303502</v>
+        <v>6.380829143493192</v>
       </c>
       <c r="D10" t="n">
-        <v>39.55292311201698</v>
+        <v>6.42735000570276</v>
       </c>
       <c r="E10" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F10" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.65789493891246</v>
+        <v>6.606907927573275</v>
       </c>
       <c r="D11" t="n">
-        <v>41.05095583991327</v>
+        <v>6.670780323985907</v>
       </c>
       <c r="E11" t="n">
-        <v>13.18382726846639</v>
+        <v>2.142371931125788</v>
       </c>
       <c r="F11" t="n">
-        <v>13.26613688155731</v>
+        <v>2.155747243253063</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
